--- a/Server/NewServer/bin/commonconfig/setting/gm_log_note.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/gm_log_note.xlsx
@@ -35,7 +35,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -46,7 +46,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-取值范围</t>
+Allowed range</t>
         </r>
         <r>
           <rPr>
